--- a/analysis/dataview/formula.xlsx
+++ b/analysis/dataview/formula.xlsx
@@ -9,19 +9,20 @@
   <sheets>
     <sheet name="Unique Variants" sheetId="1" r:id="rId1"/>
     <sheet name="SubTask" sheetId="2" r:id="rId2"/>
-    <sheet name="Format" sheetId="3" r:id="rId3"/>
-    <sheet name="Length" sheetId="4" r:id="rId4"/>
-    <sheet name="ModelFamily" sheetId="5" r:id="rId5"/>
-    <sheet name="ModelName" sheetId="6" r:id="rId6"/>
-    <sheet name="Symbol" sheetId="7" r:id="rId7"/>
-    <sheet name="Value" sheetId="8" r:id="rId8"/>
+    <sheet name="ExampleType" sheetId="3" r:id="rId3"/>
+    <sheet name="Format" sheetId="4" r:id="rId4"/>
+    <sheet name="Length" sheetId="5" r:id="rId5"/>
+    <sheet name="ModelFamily" sheetId="6" r:id="rId6"/>
+    <sheet name="ModelName" sheetId="7" r:id="rId7"/>
+    <sheet name="Symbol" sheetId="8" r:id="rId8"/>
+    <sheet name="Value" sheetId="9" r:id="rId9"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="64">
   <si>
     <t>Unique Variants</t>
   </si>
@@ -68,6 +69,15 @@
     <t>equivalent</t>
   </si>
   <si>
+    <t>FewShot</t>
+  </si>
+  <si>
+    <t>OneShot</t>
+  </si>
+  <si>
+    <t>ZeroShot</t>
+  </si>
+  <si>
     <t>format1_infix_format2_infix</t>
   </si>
   <si>
@@ -111,6 +121,9 @@
   </si>
   <si>
     <t>medium</t>
+  </si>
+  <si>
+    <t>max</t>
   </si>
   <si>
     <t>01-ai</t>
@@ -579,7 +592,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -673,10 +686,10 @@
         <v>13</v>
       </c>
       <c r="B3">
-        <v>44.37956790123457</v>
+        <v>44.3210524691358</v>
       </c>
       <c r="C3">
-        <v>37.78946558294356</v>
+        <v>37.79965096074658</v>
       </c>
       <c r="D3">
         <v>3240</v>
@@ -687,10 +700,10 @@
         <v>14</v>
       </c>
       <c r="B4">
-        <v>88.88919547325102</v>
+        <v>53.63596296296296</v>
       </c>
       <c r="C4">
-        <v>27.05038461522708</v>
+        <v>24.05874642712387</v>
       </c>
       <c r="D4">
         <v>4860</v>
@@ -703,12 +716,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
@@ -725,13 +738,13 @@
         <v>15</v>
       </c>
       <c r="B2">
-        <v>90.03340740740741</v>
+        <v>52.66565020576132</v>
       </c>
       <c r="C2">
-        <v>26.28187624896303</v>
+        <v>30.78952096016151</v>
       </c>
       <c r="D2">
-        <v>540</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -739,13 +752,13 @@
         <v>16</v>
       </c>
       <c r="B3">
-        <v>72.33427777777779</v>
+        <v>48.52816872427984</v>
       </c>
       <c r="C3">
-        <v>37.85317482747804</v>
+        <v>29.88028771334444</v>
       </c>
       <c r="D3">
-        <v>1080</v>
+        <v>2916</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -753,139 +766,13 @@
         <v>17</v>
       </c>
       <c r="B4">
-        <v>69.30060185185185</v>
+        <v>36.19691769547325</v>
       </c>
       <c r="C4">
-        <v>36.90815888548011</v>
+        <v>28.82027969506444</v>
       </c>
       <c r="D4">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5">
-        <v>67.96403703703704</v>
-      </c>
-      <c r="C5">
-        <v>39.72552502201585</v>
-      </c>
-      <c r="D5">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B6">
-        <v>89.09281481481482</v>
-      </c>
-      <c r="C6">
-        <v>26.91141562858546</v>
-      </c>
-      <c r="D6">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7">
-        <v>60.57078703703704</v>
-      </c>
-      <c r="C7">
-        <v>40.25409023168856</v>
-      </c>
-      <c r="D7">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B8">
-        <v>64.68331481481481</v>
-      </c>
-      <c r="C8">
-        <v>41.77521659023718</v>
-      </c>
-      <c r="D8">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B9">
-        <v>64.22788888888888</v>
-      </c>
-      <c r="C9">
-        <v>40.31265917426357</v>
-      </c>
-      <c r="D9">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10">
-        <v>88.99212962962963</v>
-      </c>
-      <c r="C10">
-        <v>27.02448938351225</v>
-      </c>
-      <c r="D10">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11">
-        <v>11.945</v>
-      </c>
-      <c r="C11">
-        <v>19.11952036042264</v>
-      </c>
-      <c r="D11">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="B12">
-        <v>2.207333333333334</v>
-      </c>
-      <c r="C12">
-        <v>4.820168081504188</v>
-      </c>
-      <c r="D12">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B13">
-        <v>1.831962962962963</v>
-      </c>
-      <c r="C13">
-        <v>4.370862946018133</v>
-      </c>
-      <c r="D13">
-        <v>540</v>
+        <v>2430</v>
       </c>
     </row>
   </sheetData>
@@ -895,12 +782,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
@@ -914,44 +801,170 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="B2">
-        <v>65.70167592592593</v>
+        <v>74.63194444444444</v>
       </c>
       <c r="C2">
-        <v>40.62235106807776</v>
+        <v>27.48408163531075</v>
       </c>
       <c r="D2">
-        <v>3240</v>
+        <v>540</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="B3">
-        <v>55.7739537037037</v>
+        <v>51.93455555555555</v>
       </c>
       <c r="C3">
-        <v>44.51853935700653</v>
+        <v>31.4246213745304</v>
       </c>
       <c r="D3">
-        <v>3240</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4">
+        <v>48.33165740740741</v>
+      </c>
+      <c r="C4">
+        <v>28.47988546210151</v>
+      </c>
+      <c r="D4">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5">
+        <v>46.61683333333333</v>
+      </c>
+      <c r="C5">
+        <v>30.70383262824074</v>
+      </c>
+      <c r="D5">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6">
+        <v>65.13698148148148</v>
+      </c>
+      <c r="C6">
+        <v>27.12888887950244</v>
+      </c>
+      <c r="D6">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7">
+        <v>39.99675925925926</v>
+      </c>
+      <c r="C7">
+        <v>26.72088401072384</v>
+      </c>
+      <c r="D7">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8">
+        <v>43.53302777777778</v>
+      </c>
+      <c r="C8">
+        <v>31.15697741010503</v>
+      </c>
+      <c r="D8">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9">
+        <v>43.11360185185185</v>
+      </c>
+      <c r="C9">
+        <v>29.19994724767025</v>
+      </c>
+      <c r="D9">
+        <v>1080</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10">
+        <v>61.82818518518518</v>
+      </c>
+      <c r="C10">
+        <v>25.80071001962279</v>
+      </c>
+      <c r="D10">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B11">
+        <v>11.945</v>
+      </c>
+      <c r="C11">
+        <v>19.11952036042264</v>
+      </c>
+      <c r="D11">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12">
+        <v>2.207333333333334</v>
+      </c>
+      <c r="C12">
+        <v>4.820168081504188</v>
+      </c>
+      <c r="D12">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B4">
-        <v>58.90178086419753</v>
-      </c>
-      <c r="C4">
-        <v>43.72895715076204</v>
-      </c>
-      <c r="D4">
-        <v>3240</v>
+      <c r="B13">
+        <v>1.831962962962963</v>
+      </c>
+      <c r="C13">
+        <v>4.370862946018133</v>
+      </c>
+      <c r="D13">
+        <v>540</v>
       </c>
     </row>
   </sheetData>
@@ -961,12 +974,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
@@ -983,13 +996,13 @@
         <v>30</v>
       </c>
       <c r="B2">
-        <v>72.72882716049382</v>
+        <v>47.86718518518519</v>
       </c>
       <c r="C2">
-        <v>37.43868791844341</v>
+        <v>32.23923908260178</v>
       </c>
       <c r="D2">
-        <v>486</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -997,13 +1010,13 @@
         <v>31</v>
       </c>
       <c r="B3">
-        <v>53.13097736625515</v>
+        <v>38.14845679012345</v>
       </c>
       <c r="C3">
-        <v>41.7426831596086</v>
+        <v>32.63681024618324</v>
       </c>
       <c r="D3">
-        <v>2916</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1011,111 +1024,13 @@
         <v>32</v>
       </c>
       <c r="B4">
-        <v>63.38125514403292</v>
+        <v>41.42340432098765</v>
       </c>
       <c r="C4">
-        <v>41.18987243491865</v>
+        <v>33.21155314941757</v>
       </c>
       <c r="D4">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5">
-        <v>2.769465020576132</v>
-      </c>
-      <c r="C5">
-        <v>7.05469355510967</v>
-      </c>
-      <c r="D5">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6">
-        <v>82.985329218107</v>
-      </c>
-      <c r="C6">
-        <v>33.87439840671961</v>
-      </c>
-      <c r="D6">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7">
-        <v>54.17827160493827</v>
-      </c>
-      <c r="C7">
-        <v>46.92496435247148</v>
-      </c>
-      <c r="D7">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8">
-        <v>61.04976954732511</v>
-      </c>
-      <c r="C8">
-        <v>43.78016695628313</v>
-      </c>
-      <c r="D8">
-        <v>2430</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B9">
-        <v>69.92732510288066</v>
-      </c>
-      <c r="C9">
-        <v>39.33219859654962</v>
-      </c>
-      <c r="D9">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B10">
-        <v>69.92730452674897</v>
-      </c>
-      <c r="C10">
-        <v>37.60029131190426</v>
-      </c>
-      <c r="D10">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B11">
-        <v>81.29179012345679</v>
-      </c>
-      <c r="C11">
-        <v>34.81380857419907</v>
-      </c>
-      <c r="D11">
-        <v>972</v>
+        <v>3240</v>
       </c>
     </row>
   </sheetData>
@@ -1125,301 +1040,224 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6">
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2">
+        <v>51.28220164609053</v>
+      </c>
+      <c r="D2">
+        <v>28.37268336859439</v>
+      </c>
+      <c r="E2">
+        <v>486</v>
+      </c>
+      <c r="F2">
+        <v>51.28220164609053</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3">
+        <v>37.1151817558299</v>
+      </c>
+      <c r="D3">
+        <v>30.95987688069529</v>
+      </c>
+      <c r="E3">
+        <v>2916</v>
+      </c>
+      <c r="F3">
+        <v>61.50703703703704</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1">
+        <v>2</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4">
+        <v>40.17018518518518</v>
+      </c>
+      <c r="D4">
+        <v>24.32489351046644</v>
+      </c>
+      <c r="E4">
+        <v>486</v>
+      </c>
+      <c r="F4">
+        <v>48.32221536351165</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1">
+        <v>3</v>
+      </c>
+      <c r="B5" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5">
+        <v>1.392510288065844</v>
+      </c>
+      <c r="D5">
+        <v>3.79464846651571</v>
+      </c>
+      <c r="E5">
+        <v>486</v>
+      </c>
+      <c r="F5">
+        <v>1.392510288065844</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>4</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6">
+        <v>66.77779835390947</v>
+      </c>
+      <c r="D6">
+        <v>33.42214745499733</v>
+      </c>
+      <c r="E6">
+        <v>486</v>
+      </c>
+      <c r="F6">
+        <v>66.77779835390947</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>5</v>
+      </c>
+      <c r="B7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C7">
+        <v>31.71874485596708</v>
+      </c>
+      <c r="D7">
+        <v>27.72575967499152</v>
+      </c>
+      <c r="E7">
+        <v>486</v>
+      </c>
+      <c r="F7">
+        <v>31.71874485596708</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B8" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8">
+        <v>41.16384773662551</v>
+      </c>
+      <c r="D8">
+        <v>31.98807284621637</v>
+      </c>
+      <c r="E8">
+        <v>2430</v>
+      </c>
+      <c r="F8">
+        <v>63.45413580246913</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9">
+        <v>51.6304938271605</v>
+      </c>
+      <c r="D9">
+        <v>31.71041429898645</v>
+      </c>
+      <c r="E9">
+        <v>486</v>
+      </c>
+      <c r="F9">
+        <v>51.6304938271605</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>42</v>
+      </c>
+      <c r="C10">
+        <v>49.69958847736626</v>
+      </c>
+      <c r="D10">
+        <v>27.79649846366642</v>
+      </c>
+      <c r="E10">
+        <v>486</v>
+      </c>
+      <c r="F10">
+        <v>49.69958847736626</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2">
-        <v>2.769465020576132</v>
-      </c>
-      <c r="C2">
-        <v>7.05469355510967</v>
-      </c>
-      <c r="D2">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3">
-        <v>78.90187242798353</v>
-      </c>
-      <c r="C3">
-        <v>34.88878754681485</v>
-      </c>
-      <c r="D3">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B4">
-        <v>68.86679012345679</v>
-      </c>
-      <c r="C4">
-        <v>40.02095361987917</v>
-      </c>
-      <c r="D4">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="1" t="s">
+      <c r="B11" t="s">
         <v>43</v>
       </c>
-      <c r="B5">
-        <v>49.20318930041152</v>
-      </c>
-      <c r="C5">
-        <v>48.99671753694342</v>
-      </c>
-      <c r="D5">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6">
-        <v>54.28137860082305</v>
-      </c>
-      <c r="C6">
-        <v>46.51733421230469</v>
-      </c>
-      <c r="D6">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B7">
-        <v>53.99561728395062</v>
-      </c>
-      <c r="C7">
-        <v>39.98614091775377</v>
-      </c>
-      <c r="D7">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8">
-        <v>69.92730452674897</v>
-      </c>
-      <c r="C8">
-        <v>37.60029131190426</v>
-      </c>
-      <c r="D8">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B9">
-        <v>69.92732510288066</v>
-      </c>
-      <c r="C9">
-        <v>39.33219859654962</v>
-      </c>
-      <c r="D9">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B10">
-        <v>20.45691358024691</v>
-      </c>
-      <c r="C10">
-        <v>26.76507122869379</v>
-      </c>
-      <c r="D10">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B11">
-        <v>52.19722222222222</v>
-      </c>
       <c r="C11">
-        <v>48.22542048471778</v>
+        <v>64.2058950617284</v>
       </c>
       <c r="D11">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12">
-        <v>28.18880658436214</v>
-      </c>
-      <c r="C12">
-        <v>22.12008507971087</v>
-      </c>
-      <c r="D12">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13">
-        <v>70.75559670781894</v>
-      </c>
-      <c r="C13">
-        <v>36.54972431043739</v>
-      </c>
-      <c r="D13">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B14">
-        <v>78.15773662551442</v>
-      </c>
-      <c r="C14">
-        <v>35.08177415932015</v>
-      </c>
-      <c r="D14">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B15">
-        <v>69.02958847736625</v>
-      </c>
-      <c r="C15">
-        <v>38.58046997831709</v>
-      </c>
-      <c r="D15">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B16">
-        <v>72.72882716049382</v>
-      </c>
-      <c r="C16">
-        <v>37.43868791844341</v>
-      </c>
-      <c r="D16">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B17">
-        <v>82.985329218107</v>
-      </c>
-      <c r="C17">
-        <v>33.87439840671961</v>
-      </c>
-      <c r="D17">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B18">
-        <v>63.38125514403292</v>
-      </c>
-      <c r="C18">
-        <v>41.18987243491865</v>
-      </c>
-      <c r="D18">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B19">
-        <v>81.79825102880658</v>
-      </c>
-      <c r="C19">
-        <v>35.0422037099883</v>
-      </c>
-      <c r="D19">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B20">
-        <v>80.78532921810699</v>
-      </c>
-      <c r="C20">
-        <v>34.61259023353925</v>
-      </c>
-      <c r="D20">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B21">
-        <v>54.17827160493827</v>
-      </c>
-      <c r="C21">
-        <v>46.92496435247148</v>
-      </c>
-      <c r="D21">
-        <v>486</v>
+        <v>31.92848522584475</v>
+      </c>
+      <c r="E11">
+        <v>972</v>
+      </c>
+      <c r="F11">
+        <v>64.38788065843622</v>
       </c>
     </row>
   </sheetData>
@@ -1429,12 +1267,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
@@ -1448,44 +1286,282 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="B2">
-        <v>60.35683950617284</v>
+        <v>1.392510288065844</v>
       </c>
       <c r="C2">
-        <v>43.10165829206512</v>
+        <v>3.79464846651571</v>
       </c>
       <c r="D2">
-        <v>3240</v>
+        <v>486</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="B3">
-        <v>59.98282716049382</v>
+        <v>63.45413580246913</v>
       </c>
       <c r="C3">
-        <v>43.1450830163194</v>
+        <v>32.31487222601353</v>
       </c>
       <c r="D3">
-        <v>3240</v>
+        <v>486</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="B4">
-        <v>60.0377438271605</v>
+        <v>51.8362962962963</v>
       </c>
       <c r="C4">
-        <v>43.31867727013967</v>
+        <v>32.43729715732881</v>
       </c>
       <c r="D4">
-        <v>3240</v>
+        <v>486</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5">
+        <v>25.22246913580247</v>
+      </c>
+      <c r="C5">
+        <v>25.8488273851981</v>
+      </c>
+      <c r="D5">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6">
+        <v>31.68084362139918</v>
+      </c>
+      <c r="C6">
+        <v>26.26337684313199</v>
+      </c>
+      <c r="D6">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7">
+        <v>33.62549382716049</v>
+      </c>
+      <c r="C7">
+        <v>25.62306344430922</v>
+      </c>
+      <c r="D7">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B8">
+        <v>49.69958847736626</v>
+      </c>
+      <c r="C8">
+        <v>27.79649846366642</v>
+      </c>
+      <c r="D8">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9">
+        <v>51.6304938271605</v>
+      </c>
+      <c r="C9">
+        <v>31.71041429898645</v>
+      </c>
+      <c r="D9">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10">
+        <v>11.50965020576132</v>
+      </c>
+      <c r="C10">
+        <v>15.88778086147131</v>
+      </c>
+      <c r="D10">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11">
+        <v>29.89543209876543</v>
+      </c>
+      <c r="C11">
+        <v>27.55735187924288</v>
+      </c>
+      <c r="D11">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12">
+        <v>20.36965020576132</v>
+      </c>
+      <c r="C12">
+        <v>16.40165191834615</v>
+      </c>
+      <c r="D12">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13">
+        <v>48.23465020576132</v>
+      </c>
+      <c r="C13">
+        <v>24.79132312835908</v>
+      </c>
+      <c r="D13">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B14">
+        <v>61.50703703703704</v>
+      </c>
+      <c r="C14">
+        <v>32.4300160355916</v>
+      </c>
+      <c r="D14">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15">
+        <v>51.17467078189301</v>
+      </c>
+      <c r="C15">
+        <v>30.09027102752563</v>
+      </c>
+      <c r="D15">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B16">
+        <v>51.28220164609053</v>
+      </c>
+      <c r="C16">
+        <v>28.37268336859439</v>
+      </c>
+      <c r="D16">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B17">
+        <v>66.77779835390947</v>
+      </c>
+      <c r="C17">
+        <v>33.42214745499733</v>
+      </c>
+      <c r="D17">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18">
+        <v>40.17018518518518</v>
+      </c>
+      <c r="C18">
+        <v>24.32489351046644</v>
+      </c>
+      <c r="D18">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19">
+        <v>64.38788065843622</v>
+      </c>
+      <c r="C19">
+        <v>32.01215741729135</v>
+      </c>
+      <c r="D19">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B20">
+        <v>64.02390946502058</v>
+      </c>
+      <c r="C20">
+        <v>31.87653768506957</v>
+      </c>
+      <c r="D20">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21">
+        <v>31.71874485596708</v>
+      </c>
+      <c r="C21">
+        <v>27.72575967499152</v>
+      </c>
+      <c r="D21">
+        <v>486</v>
       </c>
     </row>
   </sheetData>
@@ -1500,7 +1576,7 @@
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>9</v>
@@ -1514,13 +1590,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B2">
-        <v>60.50175</v>
+        <v>42.76104938271605</v>
       </c>
       <c r="C2">
-        <v>42.68542491034778</v>
+        <v>32.96018330770794</v>
       </c>
       <c r="D2">
         <v>3240</v>
@@ -1528,13 +1604,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B3">
-        <v>59.68348148148149</v>
+        <v>42.44020679012345</v>
       </c>
       <c r="C3">
-        <v>43.67539076580196</v>
+        <v>32.87276316719996</v>
       </c>
       <c r="D3">
         <v>3240</v>
@@ -1542,13 +1618,79 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B4">
-        <v>60.19217901234568</v>
+        <v>42.23779012345679</v>
       </c>
       <c r="C4">
-        <v>43.19622416411509</v>
+        <v>33.00486603648355</v>
+      </c>
+      <c r="D4">
+        <v>3240</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2">
+        <v>42.76644135802469</v>
+      </c>
+      <c r="C2">
+        <v>32.45626322163545</v>
+      </c>
+      <c r="D2">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3">
+        <v>42.22247222222222</v>
+      </c>
+      <c r="C3">
+        <v>33.37810331657398</v>
+      </c>
+      <c r="D3">
+        <v>3240</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4">
+        <v>42.45013271604938</v>
+      </c>
+      <c r="C4">
+        <v>32.99691795015091</v>
       </c>
       <c r="D4">
         <v>3240</v>
